--- a/data/trans_bre/DC-Edad-trans_bre.xlsx
+++ b/data/trans_bre/DC-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 21,05</t>
+          <t>12,81; 21,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 16,44</t>
+          <t>8,11; 16,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 11,74</t>
+          <t>5,43; 11,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 24,3</t>
+          <t>8,08; 23,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>225,32; 708,6</t>
+          <t>211,23; 695,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>150,71; 622,52</t>
+          <t>139,14; 648,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>184,87; 1877,73</t>
+          <t>202,41; 1840,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>65,49; 516,42</t>
+          <t>54,06; 498,37</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,96; 19,83</t>
+          <t>11,82; 19,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 12,38</t>
+          <t>5,76; 12,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,46</t>
+          <t>6,66; 13,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,64; 51,15</t>
+          <t>14,93; 52,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>113,79; 276,35</t>
+          <t>114,25; 276,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,88; 278,3</t>
+          <t>81,42; 267,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>126,22; 541,56</t>
+          <t>122,41; 502,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>122,04; 647,52</t>
+          <t>122,93; 688,43</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 11,06</t>
+          <t>2,64; 11,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 16,42</t>
+          <t>9,06; 16,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 8,48</t>
+          <t>1,88; 8,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 18,21</t>
+          <t>5,7; 18,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 82,03</t>
+          <t>13,89; 83,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>95,61; 267,51</t>
+          <t>99,84; 281,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,92; 152,71</t>
+          <t>22,08; 154,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,9; 148,55</t>
+          <t>39,52; 148,14</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 11,66</t>
+          <t>1,72; 12,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 15,32</t>
+          <t>7,07; 15,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 11,07</t>
+          <t>3,38; 10,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,95; 30,44</t>
+          <t>10,14; 29,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 61,88</t>
+          <t>7,46; 66,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,61; 187,05</t>
+          <t>59,51; 193,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,53; 139,22</t>
+          <t>29,27; 133,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,08; 401,23</t>
+          <t>40,57; 338,92</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 4,95</t>
+          <t>-7,85; 5,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,15; 21,11</t>
+          <t>9,64; 21,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,35; 15,0</t>
+          <t>3,96; 14,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 18,98</t>
+          <t>9,59; 18,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 16,97</t>
+          <t>-22,3; 20,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,54; 190,05</t>
+          <t>63,12; 194,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,28; 122,37</t>
+          <t>22,57; 117,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,67; 73,24</t>
+          <t>29,58; 70,98</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,83; 20,26</t>
+          <t>7,24; 21,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 20,35</t>
+          <t>6,05; 20,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 14,35</t>
+          <t>1,84; 14,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,23; 58,06</t>
+          <t>15,92; 56,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,51; 84,99</t>
+          <t>23,22; 93,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,7; 115,91</t>
+          <t>23,92; 122,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,32; 108,51</t>
+          <t>7,55; 112,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52,71; 219,93</t>
+          <t>50,8; 208,97</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 8,58</t>
+          <t>-7,28; 9,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,02; 24,45</t>
+          <t>8,96; 24,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 16,87</t>
+          <t>2,53; 16,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,23; 23,79</t>
+          <t>11,91; 23,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 27,85</t>
+          <t>-17,37; 30,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,45; 115,41</t>
+          <t>29,16; 114,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,7; 90,6</t>
+          <t>10,25; 84,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27,09; 64,25</t>
+          <t>26,3; 63,42</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,38</t>
+          <t>8,41; 12,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,66; 15,19</t>
+          <t>11,77; 15,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,15; 10,48</t>
+          <t>7,4; 10,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,76; 32,93</t>
+          <t>16,58; 32,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,37; 75,35</t>
+          <t>45,17; 74,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>103,9; 159,46</t>
+          <t>105,42; 160,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,34; 121,69</t>
+          <t>71,56; 121,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>76,87; 186,06</t>
+          <t>78,21; 180,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/DC-Edad-trans_bre.xlsx
+++ b/data/trans_bre/DC-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,33</t>
+          <t>16,59</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>208,75%</t>
+          <t>202,98%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,81; 21,11</t>
+          <t>13,09; 21,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,11; 16,18</t>
+          <t>8,13; 16,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,89</t>
+          <t>5,54; 12,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,08; 23,91</t>
+          <t>8,72; 24,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>211,23; 695,71</t>
+          <t>217,17; 720,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>139,14; 648,8</t>
+          <t>140,29; 664,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>202,41; 1840,06</t>
+          <t>196,12; 1818,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,06; 498,37</t>
+          <t>71,45; 495,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,67</t>
+          <t>15,58</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>268,05%</t>
+          <t>155,07%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 19,95</t>
+          <t>11,99; 20,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 12,37</t>
+          <t>5,59; 12,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,4</t>
+          <t>6,78; 13,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,93; 52,03</t>
+          <t>10,46; 20,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>114,25; 276,33</t>
+          <t>114,35; 289,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,42; 267,48</t>
+          <t>76,57; 279,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>122,41; 502,4</t>
+          <t>133,66; 544,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>122,93; 688,43</t>
+          <t>81,83; 279,94</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,49</t>
+          <t>17,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>124,04%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,67</t>
+          <t>2,87; 11,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,06; 16,39</t>
+          <t>8,71; 16,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,71</t>
+          <t>1,99; 8,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 18,48</t>
+          <t>12,51; 21,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,89; 83,1</t>
+          <t>15,71; 84,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99,84; 281,99</t>
+          <t>96,84; 285,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,08; 154,88</t>
+          <t>22,66; 142,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,52; 148,14</t>
+          <t>79,44; 184,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,29</t>
+          <t>14,2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>105,9%</t>
+          <t>60,81%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 12,24</t>
+          <t>1,17; 11,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 15,77</t>
+          <t>6,86; 15,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 10,76</t>
+          <t>3,18; 10,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,14; 29,92</t>
+          <t>9,74; 18,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 66,65</t>
+          <t>3,8; 62,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,51; 193,11</t>
+          <t>56,76; 188,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,27; 133,38</t>
+          <t>26,78; 132,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,57; 338,92</t>
+          <t>37,55; 88,64</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,2</t>
+          <t>15,25</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 5,57</t>
+          <t>-8,57; 4,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,64; 21,3</t>
+          <t>10,11; 21,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 14,71</t>
+          <t>4,41; 15,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,59; 18,94</t>
+          <t>10,77; 19,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 20,01</t>
+          <t>-23,5; 16,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,12; 194,32</t>
+          <t>63,36; 191,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,57; 117,19</t>
+          <t>22,9; 119,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,58; 70,98</t>
+          <t>34,51; 75,49</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35,52</t>
+          <t>19,33</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>119,24%</t>
+          <t>65,31%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,24; 21,15</t>
+          <t>6,32; 20,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,05; 20,67</t>
+          <t>6,69; 20,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 14,61</t>
+          <t>2,19; 14,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,92; 56,74</t>
+          <t>14,62; 25,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,22; 93,79</t>
+          <t>19,23; 88,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,92; 122,29</t>
+          <t>25,97; 126,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,55; 112,41</t>
+          <t>11,08; 110,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50,8; 208,97</t>
+          <t>43,66; 94,86</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,57</t>
+          <t>17,75</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 9,35</t>
+          <t>-7,59; 9,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,96; 24,81</t>
+          <t>8,68; 24,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 16,18</t>
+          <t>2,56; 16,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,91; 23,71</t>
+          <t>12,09; 23,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 30,0</t>
+          <t>-18,27; 29,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,16; 114,62</t>
+          <t>26,84; 112,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,25; 84,01</t>
+          <t>8,79; 83,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,3; 63,42</t>
+          <t>26,0; 60,74</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22,16</t>
+          <t>17,33</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>109,71%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,31</t>
+          <t>8,42; 12,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,77; 15,3</t>
+          <t>11,67; 15,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,77</t>
+          <t>7,18; 10,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,58; 32,31</t>
+          <t>15,32; 19,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,17; 74,5</t>
+          <t>45,86; 73,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>105,42; 160,14</t>
+          <t>104,6; 158,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,56; 121,28</t>
+          <t>69,92; 122,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>78,21; 180,52</t>
+          <t>67,67; 94,67</t>
         </is>
       </c>
     </row>
